--- a/3rd_year.xlsx
+++ b/3rd_year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\CUB_LOG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CUB_LOG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA36189C-6FD8-483B-9464-5305F91DADE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D529AC5-FBF1-4DCB-B77A-C4A153195BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{79A3634F-9DC4-4FF6-83CB-130307930B44}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{79A3634F-9DC4-4FF6-83CB-130307930B44}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -104,9 +104,6 @@
     <t>Dr.Premalatha</t>
   </si>
   <si>
-    <t>Dr.G.Manikandan</t>
-  </si>
-  <si>
     <t>sno</t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>problem statement no.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.G.Manikandan , Dr.Emily Jenifer </t>
   </si>
 </sst>
 </file>
@@ -553,19 +553,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -834,7 +834,7 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E17" s="4">
         <v>4</v>
@@ -851,7 +851,7 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E18" s="4">
         <v>4</v>
@@ -868,7 +868,7 @@
         <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E19" s="4">
         <v>4</v>
